--- a/완제품 등록.xlsx
+++ b/완제품 등록.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{E321D9E6-740D-4299-8B1D-5017CBD615E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DDE6DAA-795E-41CC-8495-6862915CC0C0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DDE6DAA-795E-41CC-8495-6862915CC0C0}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="182" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -312,11 +312,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -329,73 +329,16 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -723,12 +666,11 @@
     <col min="5" max="5" width="46.5703125" customWidth="1"/>
     <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5703125" customWidth="1"/>
-    <col min="9" max="9" width="24.5703125" style="14" customWidth="1"/>
+    <col min="8" max="9" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -749,15 +691,15 @@
       <c r="G1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -778,213 +720,213 @@
       <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="6">
         <v>70</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="7">
         <v>150</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="7">
         <v>50</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="7">
         <v>50</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="7">
         <v>5</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="7">
         <v>5</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="6">
         <v>4</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="6">
         <v>3</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="6" t="s">
         <v>54</v>
       </c>
     </row>
